--- a/raw/trektellen/Trektellen_headerdata_2422_2023.xlsx
+++ b/raw/trektellen/Trektellen_headerdata_2422_2023.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="848">
   <si>
     <t>id</t>
   </si>
@@ -75,6 +75,12 @@
   </si>
   <si>
     <t>temperature</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>hpa</t>
   </si>
   <si>
     <t>observersactive</t>
@@ -2891,10 +2897,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AB133"/>
+  <dimension ref="A1:AD133"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:30">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2979,8 +2985,14 @@
       <c r="AB1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:28">
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30">
       <c r="A2">
         <v>2443200</v>
       </c>
@@ -3003,21 +3015,15 @@
         <v>2023</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="s">
         <v>33</v>
       </c>
       <c r="Y2" t="s">
@@ -3030,10 +3036,16 @@
         <v>36</v>
       </c>
       <c r="AB2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30">
       <c r="A3">
         <v>2443199</v>
       </c>
@@ -3056,34 +3068,34 @@
         <v>2023</v>
       </c>
       <c r="H3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K3" t="s">
-        <v>39</v>
-      </c>
-      <c r="W3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="Y3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AB3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30">
       <c r="A4">
         <v>2443451</v>
       </c>
@@ -3106,37 +3118,37 @@
         <v>2023</v>
       </c>
       <c r="H4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K4" t="s">
-        <v>44</v>
-      </c>
-      <c r="W4" t="s">
-        <v>32</v>
-      </c>
-      <c r="X4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Y4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="Z4" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="AA4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AB4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30">
       <c r="A5">
         <v>2443771</v>
       </c>
@@ -3159,37 +3171,37 @@
         <v>2023</v>
       </c>
       <c r="H5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K5" t="s">
-        <v>51</v>
-      </c>
-      <c r="W5" t="s">
-        <v>32</v>
-      </c>
-      <c r="X5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y5" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="Z5" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AA5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30">
       <c r="A6">
         <v>2444056</v>
       </c>
@@ -3212,37 +3224,37 @@
         <v>2023</v>
       </c>
       <c r="H6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K6" t="s">
-        <v>58</v>
-      </c>
-      <c r="W6" t="s">
-        <v>32</v>
-      </c>
-      <c r="X6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Y6" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="Z6" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="AA6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AB6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30">
       <c r="A7">
         <v>2444362</v>
       </c>
@@ -3265,37 +3277,37 @@
         <v>2023</v>
       </c>
       <c r="H7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K7" t="s">
-        <v>65</v>
-      </c>
-      <c r="W7" t="s">
-        <v>32</v>
-      </c>
-      <c r="X7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Y7" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="Z7" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AA7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30">
       <c r="A8">
         <v>2444623</v>
       </c>
@@ -3318,37 +3330,37 @@
         <v>2023</v>
       </c>
       <c r="H8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K8" t="s">
-        <v>72</v>
-      </c>
-      <c r="W8" t="s">
-        <v>32</v>
-      </c>
-      <c r="X8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y8" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="Z8" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="AA8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30">
       <c r="A9">
         <v>2444941</v>
       </c>
@@ -3371,37 +3383,37 @@
         <v>2023</v>
       </c>
       <c r="H9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K9" t="s">
-        <v>78</v>
-      </c>
-      <c r="W9" t="s">
-        <v>32</v>
-      </c>
-      <c r="X9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y9" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="Z9" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="AA9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30">
       <c r="A10">
         <v>2445249</v>
       </c>
@@ -3424,37 +3436,37 @@
         <v>2023</v>
       </c>
       <c r="H10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K10" t="s">
-        <v>85</v>
-      </c>
-      <c r="W10" t="s">
-        <v>32</v>
-      </c>
-      <c r="X10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Y10" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="Z10" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="AA10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AB10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30">
       <c r="A11">
         <v>2445441</v>
       </c>
@@ -3477,37 +3489,37 @@
         <v>2023</v>
       </c>
       <c r="H11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K11" t="s">
-        <v>92</v>
-      </c>
-      <c r="W11" t="s">
-        <v>32</v>
-      </c>
-      <c r="X11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Y11" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="Z11" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="AA11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AB11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30">
       <c r="A12">
         <v>2445825</v>
       </c>
@@ -3530,37 +3542,37 @@
         <v>2023</v>
       </c>
       <c r="H12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K12" t="s">
-        <v>99</v>
-      </c>
-      <c r="W12" t="s">
-        <v>32</v>
-      </c>
-      <c r="X12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Y12" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="Z12" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="AA12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AB12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30">
       <c r="A13">
         <v>2446104</v>
       </c>
@@ -3583,37 +3595,37 @@
         <v>2023</v>
       </c>
       <c r="H13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K13" t="s">
-        <v>106</v>
-      </c>
-      <c r="W13" t="s">
-        <v>32</v>
-      </c>
-      <c r="X13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Y13" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="Z13" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="AA13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AB13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30">
       <c r="A14">
         <v>2446397</v>
       </c>
@@ -3636,34 +3648,34 @@
         <v>2023</v>
       </c>
       <c r="H14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I14" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K14" t="s">
-        <v>113</v>
-      </c>
-      <c r="W14" t="s">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="Y14" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AB14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30">
       <c r="A15">
         <v>2446665</v>
       </c>
@@ -3686,37 +3698,37 @@
         <v>2023</v>
       </c>
       <c r="H15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K15" t="s">
-        <v>119</v>
-      </c>
-      <c r="W15" t="s">
-        <v>32</v>
-      </c>
-      <c r="X15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Y15" t="s">
-        <v>121</v>
+        <v>34</v>
       </c>
       <c r="Z15" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="AA15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AB15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>124</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30">
       <c r="A16">
         <v>2446968</v>
       </c>
@@ -3739,37 +3751,37 @@
         <v>2023</v>
       </c>
       <c r="H16" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I16" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J16" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K16" t="s">
-        <v>126</v>
-      </c>
-      <c r="W16" t="s">
-        <v>32</v>
-      </c>
-      <c r="X16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y16" t="s">
-        <v>128</v>
+        <v>34</v>
       </c>
       <c r="Z16" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="AA16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AB16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>131</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30">
       <c r="A17">
         <v>2447348</v>
       </c>
@@ -3792,37 +3804,37 @@
         <v>2023</v>
       </c>
       <c r="H17" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I17" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J17" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K17" t="s">
-        <v>133</v>
-      </c>
-      <c r="W17" t="s">
-        <v>32</v>
-      </c>
-      <c r="X17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y17" t="s">
-        <v>135</v>
+        <v>34</v>
       </c>
       <c r="Z17" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="AA17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AB17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30">
       <c r="A18">
         <v>2447715</v>
       </c>
@@ -3845,43 +3857,43 @@
         <v>2023</v>
       </c>
       <c r="H18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N18" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O18">
         <v>3</v>
       </c>
-      <c r="W18" t="s">
-        <v>32</v>
-      </c>
-      <c r="X18" t="s">
-        <v>142</v>
-      </c>
       <c r="Y18" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="Z18" t="s">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="AA18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AB18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>146</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30">
       <c r="A19">
         <v>2448093</v>
       </c>
@@ -3904,34 +3916,34 @@
         <v>2023</v>
       </c>
       <c r="H19" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I19" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J19" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K19" t="s">
-        <v>148</v>
-      </c>
-      <c r="W19" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="Y19" t="s">
-        <v>149</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AB19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>152</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30">
       <c r="A20">
         <v>2448450</v>
       </c>
@@ -3954,34 +3966,34 @@
         <v>2023</v>
       </c>
       <c r="H20" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I20" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J20" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K20" t="s">
-        <v>154</v>
-      </c>
-      <c r="W20" t="s">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="Y20" t="s">
-        <v>155</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AB20" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30">
       <c r="A21">
         <v>2448895</v>
       </c>
@@ -4004,37 +4016,37 @@
         <v>2023</v>
       </c>
       <c r="H21" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I21" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J21" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K21" t="s">
-        <v>160</v>
-      </c>
-      <c r="W21" t="s">
-        <v>32</v>
-      </c>
-      <c r="X21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y21" t="s">
-        <v>162</v>
+        <v>34</v>
       </c>
       <c r="Z21" t="s">
-        <v>35</v>
+        <v>163</v>
       </c>
       <c r="AA21" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AB21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>165</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30">
       <c r="A22">
         <v>2449289</v>
       </c>
@@ -4057,34 +4069,34 @@
         <v>2023</v>
       </c>
       <c r="H22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J22" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K22" t="s">
-        <v>167</v>
-      </c>
-      <c r="W22" t="s">
-        <v>32</v>
+        <v>169</v>
       </c>
       <c r="Y22" t="s">
-        <v>168</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AB22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>171</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30">
       <c r="A23">
         <v>2449841</v>
       </c>
@@ -4107,37 +4119,37 @@
         <v>2023</v>
       </c>
       <c r="H23" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I23" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J23" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K23" t="s">
-        <v>173</v>
-      </c>
-      <c r="W23" t="s">
-        <v>32</v>
-      </c>
-      <c r="X23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y23" t="s">
-        <v>175</v>
+        <v>34</v>
       </c>
       <c r="Z23" t="s">
-        <v>35</v>
+        <v>176</v>
       </c>
       <c r="AA23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AB23" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>178</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30">
       <c r="A24">
         <v>2450291</v>
       </c>
@@ -4160,37 +4172,37 @@
         <v>2023</v>
       </c>
       <c r="H24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I24" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J24" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K24" t="s">
-        <v>180</v>
-      </c>
-      <c r="W24" t="s">
-        <v>32</v>
-      </c>
-      <c r="X24" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Y24" t="s">
-        <v>182</v>
+        <v>34</v>
       </c>
       <c r="Z24" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="AA24" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AB24" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>185</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30">
       <c r="A25">
         <v>2450786</v>
       </c>
@@ -4213,34 +4225,34 @@
         <v>2023</v>
       </c>
       <c r="H25" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I25" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J25" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K25" t="s">
-        <v>187</v>
-      </c>
-      <c r="W25" t="s">
-        <v>32</v>
+        <v>189</v>
       </c>
       <c r="Y25" t="s">
-        <v>188</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA25" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AB25" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>191</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30">
       <c r="A26">
         <v>2451737</v>
       </c>
@@ -4263,34 +4275,34 @@
         <v>2023</v>
       </c>
       <c r="H26" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I26" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J26" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K26" t="s">
-        <v>193</v>
-      </c>
-      <c r="W26" t="s">
-        <v>32</v>
+        <v>195</v>
       </c>
       <c r="Y26" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA26" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AB26" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>197</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30">
       <c r="A27">
         <v>2452133</v>
       </c>
@@ -4313,34 +4325,34 @@
         <v>2023</v>
       </c>
       <c r="H27" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I27" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J27" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K27" t="s">
-        <v>199</v>
-      </c>
-      <c r="W27" t="s">
-        <v>32</v>
+        <v>201</v>
       </c>
       <c r="Y27" t="s">
-        <v>200</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA27" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AB27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30">
       <c r="A28">
         <v>2452728</v>
       </c>
@@ -4363,34 +4375,34 @@
         <v>2023</v>
       </c>
       <c r="H28" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I28" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J28" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K28" t="s">
-        <v>205</v>
-      </c>
-      <c r="W28" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="Y28" t="s">
-        <v>206</v>
-      </c>
-      <c r="Z28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA28" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AB28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>209</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30">
       <c r="A29">
         <v>2453311</v>
       </c>
@@ -4413,37 +4425,37 @@
         <v>2023</v>
       </c>
       <c r="H29" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I29" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="J29" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K29" t="s">
-        <v>211</v>
-      </c>
-      <c r="W29" t="s">
-        <v>32</v>
-      </c>
-      <c r="X29" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Y29" t="s">
-        <v>213</v>
+        <v>34</v>
       </c>
       <c r="Z29" t="s">
-        <v>35</v>
+        <v>214</v>
       </c>
       <c r="AA29" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AB29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>216</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30">
       <c r="A30">
         <v>2453926</v>
       </c>
@@ -4466,31 +4478,31 @@
         <v>2023</v>
       </c>
       <c r="H30" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I30" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J30" t="s">
-        <v>217</v>
-      </c>
-      <c r="W30" t="s">
-        <v>32</v>
+        <v>219</v>
       </c>
       <c r="Y30" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA30" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AB30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>221</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30">
       <c r="A31">
         <v>2454455</v>
       </c>
@@ -4513,37 +4525,37 @@
         <v>2023</v>
       </c>
       <c r="H31" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I31" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J31" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K31" t="s">
-        <v>222</v>
-      </c>
-      <c r="W31" t="s">
-        <v>32</v>
-      </c>
-      <c r="X31" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Y31" t="s">
-        <v>224</v>
+        <v>34</v>
       </c>
       <c r="Z31" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="AA31" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AB31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>227</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30">
       <c r="A32">
         <v>2455050</v>
       </c>
@@ -4566,43 +4578,43 @@
         <v>2023</v>
       </c>
       <c r="H32" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I32" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J32" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K32" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O32">
         <v>4</v>
       </c>
-      <c r="W32" t="s">
-        <v>32</v>
-      </c>
-      <c r="X32" t="s">
-        <v>230</v>
-      </c>
       <c r="Y32" t="s">
-        <v>231</v>
+        <v>34</v>
       </c>
       <c r="Z32" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="AA32" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AB32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>234</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30">
       <c r="A33">
         <v>2455928</v>
       </c>
@@ -4625,34 +4637,34 @@
         <v>2023</v>
       </c>
       <c r="H33" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I33" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J33" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K33" t="s">
-        <v>236</v>
-      </c>
-      <c r="W33" t="s">
-        <v>32</v>
+        <v>238</v>
       </c>
       <c r="Y33" t="s">
-        <v>237</v>
-      </c>
-      <c r="Z33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA33" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AB33" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>240</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30">
       <c r="A34">
         <v>2456453</v>
       </c>
@@ -4675,34 +4687,34 @@
         <v>2023</v>
       </c>
       <c r="H34" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I34" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J34" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K34" t="s">
-        <v>242</v>
-      </c>
-      <c r="W34" t="s">
-        <v>32</v>
+        <v>244</v>
       </c>
       <c r="Y34" t="s">
-        <v>243</v>
-      </c>
-      <c r="Z34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA34" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AB34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>246</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30">
       <c r="A35">
         <v>2457392</v>
       </c>
@@ -4725,34 +4737,34 @@
         <v>2023</v>
       </c>
       <c r="H35" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I35" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J35" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K35" t="s">
-        <v>248</v>
-      </c>
-      <c r="W35" t="s">
-        <v>32</v>
+        <v>250</v>
       </c>
       <c r="Y35" t="s">
-        <v>249</v>
-      </c>
-      <c r="Z35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA35" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AB35" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>252</v>
+      </c>
+      <c r="AD35" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30">
       <c r="A36">
         <v>2458319</v>
       </c>
@@ -4775,34 +4787,34 @@
         <v>2023</v>
       </c>
       <c r="H36" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I36" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J36" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K36" t="s">
-        <v>254</v>
-      </c>
-      <c r="W36" t="s">
-        <v>32</v>
+        <v>256</v>
       </c>
       <c r="Y36" t="s">
-        <v>255</v>
-      </c>
-      <c r="Z36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA36" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AB36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>258</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30">
       <c r="A37">
         <v>2459210</v>
       </c>
@@ -4825,34 +4837,34 @@
         <v>2023</v>
       </c>
       <c r="H37" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I37" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J37" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K37" t="s">
-        <v>260</v>
-      </c>
-      <c r="W37" t="s">
-        <v>32</v>
+        <v>262</v>
       </c>
       <c r="Y37" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA37" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AB37" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>264</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30">
       <c r="A38">
         <v>2460005</v>
       </c>
@@ -4875,34 +4887,34 @@
         <v>2023</v>
       </c>
       <c r="H38" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I38" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J38" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K38" t="s">
-        <v>266</v>
-      </c>
-      <c r="W38" t="s">
-        <v>32</v>
+        <v>268</v>
       </c>
       <c r="Y38" t="s">
-        <v>267</v>
-      </c>
-      <c r="Z38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AB38" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>270</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30">
       <c r="A39">
         <v>2460735</v>
       </c>
@@ -4925,40 +4937,40 @@
         <v>2023</v>
       </c>
       <c r="H39" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I39" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J39" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K39" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N39" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O39">
         <v>3</v>
       </c>
-      <c r="W39" t="s">
-        <v>32</v>
-      </c>
       <c r="Y39" t="s">
-        <v>274</v>
-      </c>
-      <c r="Z39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA39" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AB39" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>277</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30">
       <c r="A40">
         <v>2461846</v>
       </c>
@@ -4981,34 +4993,34 @@
         <v>2023</v>
       </c>
       <c r="H40" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I40" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J40" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K40" t="s">
-        <v>279</v>
-      </c>
-      <c r="W40" t="s">
-        <v>32</v>
+        <v>281</v>
       </c>
       <c r="Y40" t="s">
-        <v>280</v>
-      </c>
-      <c r="Z40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA40" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AB40" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="41" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>283</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30">
       <c r="A41">
         <v>2462606</v>
       </c>
@@ -5031,34 +5043,34 @@
         <v>2023</v>
       </c>
       <c r="H41" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I41" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J41" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K41" t="s">
-        <v>284</v>
-      </c>
-      <c r="W41" t="s">
-        <v>32</v>
+        <v>286</v>
       </c>
       <c r="Y41" t="s">
-        <v>285</v>
-      </c>
-      <c r="Z41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA41" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AB41" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="42" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>288</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30">
       <c r="A42">
         <v>2463349</v>
       </c>
@@ -5081,34 +5093,34 @@
         <v>2023</v>
       </c>
       <c r="H42" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I42" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J42" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K42" t="s">
-        <v>290</v>
-      </c>
-      <c r="W42" t="s">
-        <v>32</v>
+        <v>292</v>
       </c>
       <c r="Y42" t="s">
-        <v>291</v>
-      </c>
-      <c r="Z42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA42" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AB42" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="43" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>294</v>
+      </c>
+      <c r="AD42" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30">
       <c r="A43">
         <v>2464188</v>
       </c>
@@ -5131,34 +5143,34 @@
         <v>2023</v>
       </c>
       <c r="H43" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I43" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J43" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K43" t="s">
-        <v>296</v>
-      </c>
-      <c r="W43" t="s">
-        <v>32</v>
+        <v>298</v>
       </c>
       <c r="Y43" t="s">
-        <v>297</v>
-      </c>
-      <c r="Z43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA43" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AB43" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>300</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30">
       <c r="A44">
         <v>2464741</v>
       </c>
@@ -5181,34 +5193,34 @@
         <v>2023</v>
       </c>
       <c r="H44" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I44" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J44" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="K44" t="s">
-        <v>302</v>
-      </c>
-      <c r="W44" t="s">
-        <v>32</v>
+        <v>304</v>
       </c>
       <c r="Y44" t="s">
-        <v>303</v>
-      </c>
-      <c r="Z44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA44" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AB44" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="45" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>306</v>
+      </c>
+      <c r="AD44" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30">
       <c r="A45">
         <v>2465672</v>
       </c>
@@ -5231,34 +5243,34 @@
         <v>2023</v>
       </c>
       <c r="H45" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I45" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K45" t="s">
-        <v>308</v>
-      </c>
-      <c r="W45" t="s">
-        <v>32</v>
+        <v>310</v>
       </c>
       <c r="Y45" t="s">
-        <v>309</v>
-      </c>
-      <c r="Z45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA45" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AB45" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="46" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>312</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30">
       <c r="A46">
         <v>2466330</v>
       </c>
@@ -5281,43 +5293,43 @@
         <v>2023</v>
       </c>
       <c r="H46" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I46" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J46" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K46" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N46" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O46">
         <v>8</v>
       </c>
-      <c r="W46" t="s">
-        <v>32</v>
-      </c>
-      <c r="X46" t="s">
-        <v>316</v>
-      </c>
       <c r="Y46" t="s">
-        <v>317</v>
+        <v>34</v>
       </c>
       <c r="Z46" t="s">
-        <v>35</v>
+        <v>318</v>
       </c>
       <c r="AA46" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AB46" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>320</v>
+      </c>
+      <c r="AD46" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30">
       <c r="A47">
         <v>2467354</v>
       </c>
@@ -5340,34 +5352,34 @@
         <v>2023</v>
       </c>
       <c r="H47" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I47" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J47" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K47" t="s">
-        <v>322</v>
-      </c>
-      <c r="W47" t="s">
-        <v>32</v>
+        <v>324</v>
       </c>
       <c r="Y47" t="s">
-        <v>323</v>
-      </c>
-      <c r="Z47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA47" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AB47" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="48" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>326</v>
+      </c>
+      <c r="AD47" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30">
       <c r="A48">
         <v>2468550</v>
       </c>
@@ -5390,34 +5402,34 @@
         <v>2023</v>
       </c>
       <c r="H48" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I48" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J48" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K48" t="s">
-        <v>328</v>
-      </c>
-      <c r="W48" t="s">
-        <v>32</v>
+        <v>330</v>
       </c>
       <c r="Y48" t="s">
-        <v>329</v>
-      </c>
-      <c r="Z48" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA48" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AB48" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="49" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>332</v>
+      </c>
+      <c r="AD48" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30">
       <c r="A49">
         <v>2469385</v>
       </c>
@@ -5440,37 +5452,37 @@
         <v>2023</v>
       </c>
       <c r="H49" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I49" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J49" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K49" t="s">
-        <v>334</v>
-      </c>
-      <c r="W49" t="s">
-        <v>32</v>
-      </c>
-      <c r="X49" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Y49" t="s">
-        <v>336</v>
+        <v>34</v>
       </c>
       <c r="Z49" t="s">
-        <v>35</v>
+        <v>337</v>
       </c>
       <c r="AA49" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AB49" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>339</v>
+      </c>
+      <c r="AD49" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:30">
       <c r="A50">
         <v>2470055</v>
       </c>
@@ -5493,37 +5505,37 @@
         <v>2023</v>
       </c>
       <c r="H50" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="I50" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J50" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K50" t="s">
-        <v>341</v>
-      </c>
-      <c r="W50" t="s">
-        <v>32</v>
-      </c>
-      <c r="X50" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Y50" t="s">
-        <v>343</v>
+        <v>34</v>
       </c>
       <c r="Z50" t="s">
-        <v>35</v>
+        <v>344</v>
       </c>
       <c r="AA50" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AB50" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="51" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>346</v>
+      </c>
+      <c r="AD50" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30">
       <c r="A51">
         <v>2470778</v>
       </c>
@@ -5546,37 +5558,37 @@
         <v>2023</v>
       </c>
       <c r="H51" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="I51" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J51" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K51" t="s">
-        <v>348</v>
-      </c>
-      <c r="W51" t="s">
-        <v>32</v>
-      </c>
-      <c r="X51" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Y51" t="s">
-        <v>350</v>
+        <v>34</v>
       </c>
       <c r="Z51" t="s">
-        <v>35</v>
+        <v>351</v>
       </c>
       <c r="AA51" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AB51" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>353</v>
+      </c>
+      <c r="AD51" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:30">
       <c r="A52">
         <v>2472054</v>
       </c>
@@ -5599,37 +5611,37 @@
         <v>2023</v>
       </c>
       <c r="H52" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="I52" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J52" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K52" t="s">
-        <v>355</v>
-      </c>
-      <c r="W52" t="s">
-        <v>32</v>
-      </c>
-      <c r="X52" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Y52" t="s">
-        <v>357</v>
+        <v>34</v>
       </c>
       <c r="Z52" t="s">
-        <v>35</v>
+        <v>358</v>
       </c>
       <c r="AA52" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AB52" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>360</v>
+      </c>
+      <c r="AD52" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30">
       <c r="A53">
         <v>2473099</v>
       </c>
@@ -5652,37 +5664,37 @@
         <v>2023</v>
       </c>
       <c r="H53" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="I53" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J53" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K53" t="s">
-        <v>362</v>
-      </c>
-      <c r="W53" t="s">
-        <v>32</v>
-      </c>
-      <c r="X53" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Y53" t="s">
-        <v>364</v>
+        <v>34</v>
       </c>
       <c r="Z53" t="s">
-        <v>35</v>
+        <v>365</v>
       </c>
       <c r="AA53" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AB53" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="54" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>367</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30">
       <c r="A54">
         <v>2474435</v>
       </c>
@@ -5705,34 +5717,34 @@
         <v>2023</v>
       </c>
       <c r="H54" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I54" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J54" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K54" t="s">
-        <v>369</v>
-      </c>
-      <c r="W54" t="s">
-        <v>32</v>
+        <v>371</v>
       </c>
       <c r="Y54" t="s">
-        <v>370</v>
-      </c>
-      <c r="Z54" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA54" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AB54" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="55" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>373</v>
+      </c>
+      <c r="AD54" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:30">
       <c r="A55">
         <v>2475531</v>
       </c>
@@ -5755,34 +5767,34 @@
         <v>2023</v>
       </c>
       <c r="H55" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I55" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J55" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K55" t="s">
-        <v>375</v>
-      </c>
-      <c r="W55" t="s">
-        <v>32</v>
+        <v>377</v>
       </c>
       <c r="Y55" t="s">
-        <v>376</v>
-      </c>
-      <c r="Z55" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA55" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AB55" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>379</v>
+      </c>
+      <c r="AD55" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30">
       <c r="A56">
         <v>2476536</v>
       </c>
@@ -5805,34 +5817,34 @@
         <v>2023</v>
       </c>
       <c r="H56" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="I56" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J56" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K56" t="s">
-        <v>381</v>
-      </c>
-      <c r="W56" t="s">
-        <v>32</v>
+        <v>383</v>
       </c>
       <c r="Y56" t="s">
-        <v>382</v>
-      </c>
-      <c r="Z56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA56" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AB56" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="57" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>385</v>
+      </c>
+      <c r="AD56" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30">
       <c r="A57">
         <v>2477715</v>
       </c>
@@ -5855,34 +5867,34 @@
         <v>2023</v>
       </c>
       <c r="H57" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I57" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J57" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="K57" t="s">
-        <v>387</v>
-      </c>
-      <c r="W57" t="s">
-        <v>32</v>
+        <v>389</v>
       </c>
       <c r="Y57" t="s">
-        <v>388</v>
-      </c>
-      <c r="Z57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA57" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AB57" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="58" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC57" t="s">
+        <v>391</v>
+      </c>
+      <c r="AD57" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30">
       <c r="A58">
         <v>2478655</v>
       </c>
@@ -5905,34 +5917,34 @@
         <v>2023</v>
       </c>
       <c r="H58" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="I58" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J58" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K58" t="s">
-        <v>393</v>
-      </c>
-      <c r="W58" t="s">
-        <v>32</v>
+        <v>395</v>
       </c>
       <c r="Y58" t="s">
-        <v>394</v>
-      </c>
-      <c r="Z58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA58" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AB58" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="59" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC58" t="s">
+        <v>397</v>
+      </c>
+      <c r="AD58" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30">
       <c r="A59">
         <v>2479909</v>
       </c>
@@ -5955,34 +5967,34 @@
         <v>2023</v>
       </c>
       <c r="H59" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="I59" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J59" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="K59" t="s">
-        <v>399</v>
-      </c>
-      <c r="W59" t="s">
-        <v>32</v>
+        <v>401</v>
       </c>
       <c r="Y59" t="s">
-        <v>400</v>
-      </c>
-      <c r="Z59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA59" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AB59" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="60" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC59" t="s">
+        <v>403</v>
+      </c>
+      <c r="AD59" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30">
       <c r="A60">
         <v>2481154</v>
       </c>
@@ -6005,37 +6017,37 @@
         <v>2023</v>
       </c>
       <c r="H60" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I60" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J60" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K60" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O60">
         <v>1</v>
       </c>
-      <c r="W60" t="s">
-        <v>32</v>
-      </c>
       <c r="Y60" t="s">
-        <v>406</v>
-      </c>
-      <c r="Z60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA60" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AB60" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="61" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC60" t="s">
+        <v>409</v>
+      </c>
+      <c r="AD60" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30">
       <c r="A61">
         <v>2482314</v>
       </c>
@@ -6058,34 +6070,34 @@
         <v>2023</v>
       </c>
       <c r="H61" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="I61" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J61" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K61" t="s">
-        <v>411</v>
-      </c>
-      <c r="W61" t="s">
-        <v>32</v>
+        <v>413</v>
       </c>
       <c r="Y61" t="s">
-        <v>412</v>
-      </c>
-      <c r="Z61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA61" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AB61" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="62" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC61" t="s">
+        <v>415</v>
+      </c>
+      <c r="AD61" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="1:30">
       <c r="A62">
         <v>2483139</v>
       </c>
@@ -6108,34 +6120,34 @@
         <v>2023</v>
       </c>
       <c r="H62" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="I62" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J62" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K62" t="s">
-        <v>417</v>
-      </c>
-      <c r="W62" t="s">
-        <v>32</v>
+        <v>419</v>
       </c>
       <c r="Y62" t="s">
-        <v>418</v>
-      </c>
-      <c r="Z62" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA62" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AB62" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="63" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC62" t="s">
+        <v>421</v>
+      </c>
+      <c r="AD62" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="63" spans="1:30">
       <c r="A63">
         <v>2483926</v>
       </c>
@@ -6158,37 +6170,37 @@
         <v>2023</v>
       </c>
       <c r="H63" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="I63" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="J63" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="K63" t="s">
-        <v>423</v>
-      </c>
-      <c r="W63" t="s">
-        <v>32</v>
-      </c>
-      <c r="X63" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Y63" t="s">
-        <v>425</v>
+        <v>34</v>
       </c>
       <c r="Z63" t="s">
-        <v>35</v>
+        <v>426</v>
       </c>
       <c r="AA63" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AB63" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="64" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC63" t="s">
+        <v>428</v>
+      </c>
+      <c r="AD63" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="64" spans="1:30">
       <c r="A64">
         <v>2485059</v>
       </c>
@@ -6211,34 +6223,34 @@
         <v>2023</v>
       </c>
       <c r="H64" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="I64" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="J64" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K64" t="s">
-        <v>430</v>
-      </c>
-      <c r="W64" t="s">
-        <v>32</v>
+        <v>432</v>
       </c>
       <c r="Y64" t="s">
-        <v>431</v>
-      </c>
-      <c r="Z64" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA64" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AB64" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="65" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC64" t="s">
+        <v>434</v>
+      </c>
+      <c r="AD64" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="65" spans="1:30">
       <c r="A65">
         <v>2486074</v>
       </c>
@@ -6261,34 +6273,34 @@
         <v>2023</v>
       </c>
       <c r="H65" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="I65" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J65" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K65" t="s">
-        <v>436</v>
-      </c>
-      <c r="W65" t="s">
-        <v>32</v>
+        <v>438</v>
       </c>
       <c r="Y65" t="s">
-        <v>437</v>
-      </c>
-      <c r="Z65" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA65" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AB65" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="66" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC65" t="s">
+        <v>440</v>
+      </c>
+      <c r="AD65" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66" spans="1:30">
       <c r="A66">
         <v>2487431</v>
       </c>
@@ -6311,34 +6323,34 @@
         <v>2023</v>
       </c>
       <c r="H66" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="I66" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K66" t="s">
-        <v>441</v>
-      </c>
-      <c r="W66" t="s">
-        <v>32</v>
+        <v>443</v>
       </c>
       <c r="Y66" t="s">
-        <v>442</v>
-      </c>
-      <c r="Z66" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA66" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AB66" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="67" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC66" t="s">
+        <v>445</v>
+      </c>
+      <c r="AD66" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" spans="1:30">
       <c r="A67">
         <v>2488403</v>
       </c>
@@ -6361,40 +6373,40 @@
         <v>2023</v>
       </c>
       <c r="H67" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="I67" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J67" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K67" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N67" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="O67">
         <v>3</v>
       </c>
-      <c r="W67" t="s">
-        <v>32</v>
-      </c>
       <c r="Y67" t="s">
-        <v>449</v>
-      </c>
-      <c r="Z67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA67" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AB67" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="68" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC67" t="s">
+        <v>452</v>
+      </c>
+      <c r="AD67" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68" spans="1:30">
       <c r="A68">
         <v>2489366</v>
       </c>
@@ -6417,34 +6429,34 @@
         <v>2023</v>
       </c>
       <c r="H68" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="I68" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="J68" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K68" t="s">
-        <v>453</v>
-      </c>
-      <c r="W68" t="s">
-        <v>32</v>
+        <v>455</v>
       </c>
       <c r="Y68" t="s">
-        <v>454</v>
-      </c>
-      <c r="Z68" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA68" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AB68" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="69" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC68" t="s">
+        <v>457</v>
+      </c>
+      <c r="AD68" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" spans="1:30">
       <c r="A69">
         <v>2490002</v>
       </c>
@@ -6467,37 +6479,37 @@
         <v>2023</v>
       </c>
       <c r="H69" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I69" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J69" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K69" t="s">
-        <v>459</v>
-      </c>
-      <c r="W69" t="s">
-        <v>32</v>
-      </c>
-      <c r="X69" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Y69" t="s">
-        <v>461</v>
+        <v>34</v>
       </c>
       <c r="Z69" t="s">
-        <v>35</v>
+        <v>462</v>
       </c>
       <c r="AA69" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AB69" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="70" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC69" t="s">
+        <v>464</v>
+      </c>
+      <c r="AD69" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70" spans="1:30">
       <c r="A70">
         <v>2490947</v>
       </c>
@@ -6520,34 +6532,34 @@
         <v>2023</v>
       </c>
       <c r="H70" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="I70" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J70" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="K70" t="s">
-        <v>466</v>
-      </c>
-      <c r="W70" t="s">
-        <v>32</v>
+        <v>468</v>
       </c>
       <c r="Y70" t="s">
-        <v>467</v>
-      </c>
-      <c r="Z70" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA70" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AB70" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="71" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC70" t="s">
+        <v>470</v>
+      </c>
+      <c r="AD70" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="71" spans="1:30">
       <c r="A71">
         <v>2491740</v>
       </c>
@@ -6570,34 +6582,34 @@
         <v>2023</v>
       </c>
       <c r="H71" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="I71" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J71" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K71" t="s">
-        <v>472</v>
-      </c>
-      <c r="W71" t="s">
-        <v>32</v>
+        <v>474</v>
       </c>
       <c r="Y71" t="s">
-        <v>473</v>
-      </c>
-      <c r="Z71" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA71" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AB71" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="72" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC71" t="s">
+        <v>476</v>
+      </c>
+      <c r="AD71" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="72" spans="1:30">
       <c r="A72">
         <v>2492565</v>
       </c>
@@ -6620,34 +6632,34 @@
         <v>2023</v>
       </c>
       <c r="H72" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="I72" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="J72" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K72" t="s">
-        <v>478</v>
-      </c>
-      <c r="W72" t="s">
-        <v>32</v>
+        <v>480</v>
       </c>
       <c r="Y72" t="s">
-        <v>479</v>
-      </c>
-      <c r="Z72" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA72" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AB72" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="73" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC72" t="s">
+        <v>482</v>
+      </c>
+      <c r="AD72" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30">
       <c r="A73">
         <v>2493491</v>
       </c>
@@ -6670,34 +6682,34 @@
         <v>2023</v>
       </c>
       <c r="H73" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I73" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J73" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="K73" t="s">
-        <v>484</v>
-      </c>
-      <c r="W73" t="s">
-        <v>32</v>
+        <v>486</v>
       </c>
       <c r="Y73" t="s">
-        <v>485</v>
-      </c>
-      <c r="Z73" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA73" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AB73" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="74" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC73" t="s">
+        <v>488</v>
+      </c>
+      <c r="AD73" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="74" spans="1:30">
       <c r="A74">
         <v>2494636</v>
       </c>
@@ -6720,40 +6732,40 @@
         <v>2023</v>
       </c>
       <c r="H74" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="I74" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="J74" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="K74" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="N74" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="O74">
         <v>2</v>
       </c>
-      <c r="W74" t="s">
-        <v>32</v>
-      </c>
       <c r="Y74" t="s">
-        <v>492</v>
-      </c>
-      <c r="Z74" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA74" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AB74" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="75" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC74" t="s">
+        <v>495</v>
+      </c>
+      <c r="AD74" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="75" spans="1:30">
       <c r="A75">
         <v>2495799</v>
       </c>
@@ -6776,34 +6788,34 @@
         <v>2023</v>
       </c>
       <c r="H75" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="I75" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="J75" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="K75" t="s">
-        <v>497</v>
-      </c>
-      <c r="W75" t="s">
-        <v>32</v>
+        <v>499</v>
       </c>
       <c r="Y75" t="s">
-        <v>498</v>
-      </c>
-      <c r="Z75" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA75" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AB75" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="76" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC75" t="s">
+        <v>501</v>
+      </c>
+      <c r="AD75" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="76" spans="1:30">
       <c r="A76">
         <v>2497003</v>
       </c>
@@ -6826,34 +6838,34 @@
         <v>2023</v>
       </c>
       <c r="H76" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="I76" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="J76" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K76" t="s">
-        <v>503</v>
-      </c>
-      <c r="W76" t="s">
-        <v>32</v>
+        <v>505</v>
       </c>
       <c r="Y76" t="s">
-        <v>504</v>
-      </c>
-      <c r="Z76" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA76" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AB76" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="77" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC76" t="s">
+        <v>507</v>
+      </c>
+      <c r="AD76" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="77" spans="1:30">
       <c r="A77">
         <v>2498383</v>
       </c>
@@ -6876,34 +6888,34 @@
         <v>2023</v>
       </c>
       <c r="H77" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="I77" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J77" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K77" t="s">
-        <v>509</v>
-      </c>
-      <c r="W77" t="s">
-        <v>32</v>
+        <v>511</v>
       </c>
       <c r="Y77" t="s">
-        <v>510</v>
-      </c>
-      <c r="Z77" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA77" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AB77" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="78" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC77" t="s">
+        <v>513</v>
+      </c>
+      <c r="AD77" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="78" spans="1:30">
       <c r="A78">
         <v>2499522</v>
       </c>
@@ -6926,34 +6938,34 @@
         <v>2023</v>
       </c>
       <c r="H78" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="I78" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J78" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K78" t="s">
-        <v>515</v>
-      </c>
-      <c r="W78" t="s">
-        <v>32</v>
+        <v>517</v>
       </c>
       <c r="Y78" t="s">
-        <v>516</v>
-      </c>
-      <c r="Z78" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA78" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AB78" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="79" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC78" t="s">
+        <v>519</v>
+      </c>
+      <c r="AD78" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="79" spans="1:30">
       <c r="A79">
         <v>2500524</v>
       </c>
@@ -6976,34 +6988,34 @@
         <v>2023</v>
       </c>
       <c r="H79" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="I79" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J79" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="K79" t="s">
-        <v>521</v>
-      </c>
-      <c r="W79" t="s">
-        <v>32</v>
+        <v>523</v>
       </c>
       <c r="Y79" t="s">
-        <v>522</v>
-      </c>
-      <c r="Z79" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA79" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AB79" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="80" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC79" t="s">
+        <v>525</v>
+      </c>
+      <c r="AD79" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="80" spans="1:30">
       <c r="A80">
         <v>2502403</v>
       </c>
@@ -7026,34 +7038,34 @@
         <v>2023</v>
       </c>
       <c r="H80" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="I80" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="J80" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="K80" t="s">
-        <v>527</v>
-      </c>
-      <c r="W80" t="s">
-        <v>32</v>
+        <v>529</v>
       </c>
       <c r="Y80" t="s">
-        <v>528</v>
-      </c>
-      <c r="Z80" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA80" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AB80" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="81" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC80" t="s">
+        <v>531</v>
+      </c>
+      <c r="AD80" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="81" spans="1:30">
       <c r="A81">
         <v>2503575</v>
       </c>
@@ -7076,40 +7088,40 @@
         <v>2023</v>
       </c>
       <c r="H81" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="I81" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="J81" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="K81" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="N81" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="O81">
         <v>1</v>
       </c>
-      <c r="W81" t="s">
-        <v>32</v>
-      </c>
       <c r="Y81" t="s">
-        <v>534</v>
-      </c>
-      <c r="Z81" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA81" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AB81" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="82" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC81" t="s">
+        <v>537</v>
+      </c>
+      <c r="AD81" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="82" spans="1:30">
       <c r="A82">
         <v>2505175</v>
       </c>
@@ -7132,34 +7144,34 @@
         <v>2023</v>
       </c>
       <c r="H82" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="I82" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="J82" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="K82" t="s">
-        <v>539</v>
-      </c>
-      <c r="W82" t="s">
-        <v>32</v>
+        <v>541</v>
       </c>
       <c r="Y82" t="s">
-        <v>540</v>
-      </c>
-      <c r="Z82" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA82" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AB82" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="83" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC82" t="s">
+        <v>543</v>
+      </c>
+      <c r="AD82" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="83" spans="1:30">
       <c r="A83">
         <v>2506260</v>
       </c>
@@ -7182,34 +7194,34 @@
         <v>2023</v>
       </c>
       <c r="H83" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="I83" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="J83" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="K83" t="s">
-        <v>545</v>
-      </c>
-      <c r="W83" t="s">
-        <v>32</v>
+        <v>547</v>
       </c>
       <c r="Y83" t="s">
-        <v>546</v>
-      </c>
-      <c r="Z83" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA83" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AB83" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="84" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC83" t="s">
+        <v>549</v>
+      </c>
+      <c r="AD83" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="84" spans="1:30">
       <c r="A84">
         <v>2507503</v>
       </c>
@@ -7232,34 +7244,34 @@
         <v>2023</v>
       </c>
       <c r="H84" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I84" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="J84" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="K84" t="s">
-        <v>551</v>
-      </c>
-      <c r="W84" t="s">
-        <v>32</v>
+        <v>553</v>
       </c>
       <c r="Y84" t="s">
-        <v>552</v>
-      </c>
-      <c r="Z84" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA84" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AB84" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="85" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC84" t="s">
+        <v>555</v>
+      </c>
+      <c r="AD84" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="85" spans="1:30">
       <c r="A85">
         <v>2508569</v>
       </c>
@@ -7282,34 +7294,34 @@
         <v>2023</v>
       </c>
       <c r="H85" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="I85" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="J85" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K85" t="s">
-        <v>557</v>
-      </c>
-      <c r="W85" t="s">
-        <v>32</v>
+        <v>559</v>
       </c>
       <c r="Y85" t="s">
-        <v>558</v>
-      </c>
-      <c r="Z85" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA85" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AB85" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="86" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC85" t="s">
+        <v>561</v>
+      </c>
+      <c r="AD85" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="86" spans="1:30">
       <c r="A86">
         <v>2509791</v>
       </c>
@@ -7332,34 +7344,34 @@
         <v>2023</v>
       </c>
       <c r="H86" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="I86" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="J86" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K86" t="s">
-        <v>563</v>
-      </c>
-      <c r="W86" t="s">
-        <v>32</v>
+        <v>565</v>
       </c>
       <c r="Y86" t="s">
-        <v>564</v>
-      </c>
-      <c r="Z86" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA86" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AB86" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="87" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC86" t="s">
+        <v>567</v>
+      </c>
+      <c r="AD86" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="87" spans="1:30">
       <c r="A87">
         <v>2511305</v>
       </c>
@@ -7382,34 +7394,34 @@
         <v>2023</v>
       </c>
       <c r="H87" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="I87" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="J87" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="K87" t="s">
-        <v>569</v>
-      </c>
-      <c r="W87" t="s">
-        <v>32</v>
+        <v>571</v>
       </c>
       <c r="Y87" t="s">
-        <v>570</v>
-      </c>
-      <c r="Z87" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA87" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AB87" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="88" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC87" t="s">
+        <v>573</v>
+      </c>
+      <c r="AD87" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="88" spans="1:30">
       <c r="A88">
         <v>2513142</v>
       </c>
@@ -7432,34 +7444,34 @@
         <v>2023</v>
       </c>
       <c r="H88" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="I88" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="J88" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="K88" t="s">
-        <v>575</v>
-      </c>
-      <c r="W88" t="s">
-        <v>32</v>
+        <v>577</v>
       </c>
       <c r="Y88" t="s">
-        <v>576</v>
-      </c>
-      <c r="Z88" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA88" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AB88" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="89" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC88" t="s">
+        <v>579</v>
+      </c>
+      <c r="AD88" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="89" spans="1:30">
       <c r="A89">
         <v>2514630</v>
       </c>
@@ -7482,37 +7494,37 @@
         <v>2023</v>
       </c>
       <c r="H89" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="I89" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="J89" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="K89" t="s">
-        <v>581</v>
-      </c>
-      <c r="W89" t="s">
-        <v>32</v>
-      </c>
-      <c r="X89" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="Y89" t="s">
-        <v>583</v>
+        <v>34</v>
       </c>
       <c r="Z89" t="s">
-        <v>35</v>
+        <v>584</v>
       </c>
       <c r="AA89" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB89" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="90" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC89" t="s">
+        <v>586</v>
+      </c>
+      <c r="AD89" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="90" spans="1:30">
       <c r="A90">
         <v>2516079</v>
       </c>
@@ -7535,34 +7547,34 @@
         <v>2023</v>
       </c>
       <c r="H90" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="I90" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="J90" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K90" t="s">
-        <v>588</v>
-      </c>
-      <c r="W90" t="s">
-        <v>32</v>
+        <v>590</v>
       </c>
       <c r="Y90" t="s">
-        <v>589</v>
-      </c>
-      <c r="Z90" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA90" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AB90" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="91" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC90" t="s">
+        <v>592</v>
+      </c>
+      <c r="AD90" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="91" spans="1:30">
       <c r="A91">
         <v>2517119</v>
       </c>
@@ -7585,34 +7597,34 @@
         <v>2023</v>
       </c>
       <c r="H91" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I91" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="J91" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K91" t="s">
-        <v>594</v>
-      </c>
-      <c r="W91" t="s">
-        <v>32</v>
+        <v>596</v>
       </c>
       <c r="Y91" t="s">
-        <v>595</v>
-      </c>
-      <c r="Z91" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA91" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AB91" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="92" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC91" t="s">
+        <v>598</v>
+      </c>
+      <c r="AD91" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="92" spans="1:30">
       <c r="A92">
         <v>2517981</v>
       </c>
@@ -7635,37 +7647,37 @@
         <v>2023</v>
       </c>
       <c r="H92" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="I92" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="J92" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K92" t="s">
-        <v>600</v>
-      </c>
-      <c r="W92" t="s">
-        <v>32</v>
-      </c>
-      <c r="X92" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="Y92" t="s">
-        <v>602</v>
+        <v>34</v>
       </c>
       <c r="Z92" t="s">
-        <v>35</v>
+        <v>603</v>
       </c>
       <c r="AA92" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AB92" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="93" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC92" t="s">
+        <v>605</v>
+      </c>
+      <c r="AD92" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="93" spans="1:30">
       <c r="A93">
         <v>2518997</v>
       </c>
@@ -7688,34 +7700,34 @@
         <v>2023</v>
       </c>
       <c r="H93" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="I93" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="J93" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="K93" t="s">
-        <v>607</v>
-      </c>
-      <c r="W93" t="s">
-        <v>32</v>
+        <v>609</v>
       </c>
       <c r="Y93" t="s">
-        <v>608</v>
-      </c>
-      <c r="Z93" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA93" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AB93" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="94" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC93" t="s">
+        <v>611</v>
+      </c>
+      <c r="AD93" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="94" spans="1:30">
       <c r="A94">
         <v>2520751</v>
       </c>
@@ -7738,34 +7750,34 @@
         <v>2023</v>
       </c>
       <c r="H94" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="I94" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="J94" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K94" t="s">
-        <v>613</v>
-      </c>
-      <c r="W94" t="s">
-        <v>32</v>
+        <v>615</v>
       </c>
       <c r="Y94" t="s">
-        <v>614</v>
-      </c>
-      <c r="Z94" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA94" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AB94" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="95" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC94" t="s">
+        <v>617</v>
+      </c>
+      <c r="AD94" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="95" spans="1:30">
       <c r="A95">
         <v>2522436</v>
       </c>
@@ -7788,40 +7800,40 @@
         <v>2023</v>
       </c>
       <c r="H95" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="I95" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="J95" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="K95" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="N95" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="O95">
         <v>6</v>
       </c>
-      <c r="W95" t="s">
-        <v>32</v>
-      </c>
       <c r="Y95" t="s">
-        <v>621</v>
-      </c>
-      <c r="Z95" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA95" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AB95" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="96" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC95" t="s">
+        <v>624</v>
+      </c>
+      <c r="AD95" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="96" spans="1:30">
       <c r="A96">
         <v>2523885</v>
       </c>
@@ -7844,34 +7856,34 @@
         <v>2023</v>
       </c>
       <c r="H96" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="I96" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="J96" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="K96" t="s">
-        <v>626</v>
-      </c>
-      <c r="W96" t="s">
-        <v>32</v>
+        <v>628</v>
       </c>
       <c r="Y96" t="s">
-        <v>627</v>
-      </c>
-      <c r="Z96" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA96" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AB96" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="97" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC96" t="s">
+        <v>630</v>
+      </c>
+      <c r="AD96" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="97" spans="1:30">
       <c r="A97">
         <v>2525614</v>
       </c>
@@ -7894,34 +7906,34 @@
         <v>2023</v>
       </c>
       <c r="H97" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="I97" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="J97" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="K97" t="s">
-        <v>632</v>
-      </c>
-      <c r="W97" t="s">
-        <v>32</v>
+        <v>634</v>
       </c>
       <c r="Y97" t="s">
-        <v>633</v>
-      </c>
-      <c r="Z97" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA97" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AB97" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="98" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC97" t="s">
+        <v>636</v>
+      </c>
+      <c r="AD97" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="98" spans="1:30">
       <c r="A98">
         <v>2527351</v>
       </c>
@@ -7944,34 +7956,34 @@
         <v>2023</v>
       </c>
       <c r="H98" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="I98" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="J98" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="K98" t="s">
-        <v>638</v>
-      </c>
-      <c r="W98" t="s">
-        <v>32</v>
+        <v>640</v>
       </c>
       <c r="Y98" t="s">
-        <v>639</v>
-      </c>
-      <c r="Z98" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA98" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AB98" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="99" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC98" t="s">
+        <v>642</v>
+      </c>
+      <c r="AD98" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="99" spans="1:30">
       <c r="A99">
         <v>2528510</v>
       </c>
@@ -7994,34 +8006,34 @@
         <v>2023</v>
       </c>
       <c r="H99" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="I99" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="J99" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="K99" t="s">
-        <v>644</v>
-      </c>
-      <c r="W99" t="s">
-        <v>32</v>
+        <v>646</v>
       </c>
       <c r="Y99" t="s">
-        <v>645</v>
-      </c>
-      <c r="Z99" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA99" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AB99" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="100" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC99" t="s">
+        <v>648</v>
+      </c>
+      <c r="AD99" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="100" spans="1:30">
       <c r="A100">
         <v>2529559</v>
       </c>
@@ -8044,34 +8056,34 @@
         <v>2023</v>
       </c>
       <c r="H100" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="I100" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="J100" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="K100" t="s">
-        <v>650</v>
-      </c>
-      <c r="W100" t="s">
-        <v>32</v>
+        <v>652</v>
       </c>
       <c r="Y100" t="s">
-        <v>651</v>
-      </c>
-      <c r="Z100" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA100" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AB100" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="101" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC100" t="s">
+        <v>654</v>
+      </c>
+      <c r="AD100" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="101" spans="1:30">
       <c r="A101">
         <v>2530548</v>
       </c>
@@ -8094,34 +8106,34 @@
         <v>2023</v>
       </c>
       <c r="H101" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="I101" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="J101" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="K101" t="s">
-        <v>656</v>
-      </c>
-      <c r="W101" t="s">
-        <v>32</v>
+        <v>658</v>
       </c>
       <c r="Y101" t="s">
-        <v>657</v>
-      </c>
-      <c r="Z101" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA101" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AB101" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="102" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC101" t="s">
+        <v>660</v>
+      </c>
+      <c r="AD101" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="102" spans="1:30">
       <c r="A102">
         <v>2544389</v>
       </c>
@@ -8144,37 +8156,37 @@
         <v>2023</v>
       </c>
       <c r="H102" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="I102" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="J102" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="K102" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="N102" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="O102">
         <v>5</v>
       </c>
-      <c r="W102" t="s">
-        <v>32</v>
-      </c>
       <c r="Y102" t="s">
-        <v>664</v>
-      </c>
-      <c r="Z102" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA102" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="103" spans="1:28">
+        <v>666</v>
+      </c>
+      <c r="AB102" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC102" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="103" spans="1:30">
       <c r="A103">
         <v>2532965</v>
       </c>
@@ -8197,34 +8209,34 @@
         <v>2023</v>
       </c>
       <c r="H103" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="I103" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="J103" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="K103" t="s">
-        <v>668</v>
-      </c>
-      <c r="W103" t="s">
-        <v>32</v>
+        <v>670</v>
       </c>
       <c r="Y103" t="s">
-        <v>669</v>
-      </c>
-      <c r="Z103" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA103" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AB103" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="104" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC103" t="s">
+        <v>672</v>
+      </c>
+      <c r="AD103" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="104" spans="1:30">
       <c r="A104">
         <v>2534040</v>
       </c>
@@ -8247,34 +8259,34 @@
         <v>2023</v>
       </c>
       <c r="H104" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="I104" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="J104" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K104" t="s">
-        <v>673</v>
-      </c>
-      <c r="W104" t="s">
-        <v>32</v>
+        <v>675</v>
       </c>
       <c r="Y104" t="s">
-        <v>674</v>
-      </c>
-      <c r="Z104" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA104" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AB104" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="105" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC104" t="s">
+        <v>677</v>
+      </c>
+      <c r="AD104" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="105" spans="1:30">
       <c r="A105">
         <v>2534869</v>
       </c>
@@ -8297,34 +8309,34 @@
         <v>2023</v>
       </c>
       <c r="H105" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="I105" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="J105" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="K105" t="s">
-        <v>679</v>
-      </c>
-      <c r="W105" t="s">
-        <v>32</v>
+        <v>681</v>
       </c>
       <c r="Y105" t="s">
-        <v>680</v>
-      </c>
-      <c r="Z105" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA105" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AB105" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="106" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC105" t="s">
+        <v>683</v>
+      </c>
+      <c r="AD105" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="106" spans="1:30">
       <c r="A106">
         <v>2535801</v>
       </c>
@@ -8347,34 +8359,34 @@
         <v>2023</v>
       </c>
       <c r="H106" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="I106" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="J106" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="K106" t="s">
-        <v>685</v>
-      </c>
-      <c r="W106" t="s">
-        <v>32</v>
+        <v>687</v>
       </c>
       <c r="Y106" t="s">
-        <v>686</v>
-      </c>
-      <c r="Z106" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA106" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AB106" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="107" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC106" t="s">
+        <v>689</v>
+      </c>
+      <c r="AD106" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="107" spans="1:30">
       <c r="A107">
         <v>2536428</v>
       </c>
@@ -8397,34 +8409,34 @@
         <v>2023</v>
       </c>
       <c r="H107" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="I107" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="J107" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="K107" t="s">
-        <v>691</v>
-      </c>
-      <c r="W107" t="s">
-        <v>32</v>
+        <v>693</v>
       </c>
       <c r="Y107" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z107" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA107" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AB107" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="108" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC107" t="s">
+        <v>695</v>
+      </c>
+      <c r="AD107" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="108" spans="1:30">
       <c r="A108">
         <v>2537566</v>
       </c>
@@ -8447,34 +8459,34 @@
         <v>2023</v>
       </c>
       <c r="H108" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="I108" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="J108" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="K108" t="s">
-        <v>697</v>
-      </c>
-      <c r="W108" t="s">
-        <v>32</v>
+        <v>699</v>
       </c>
       <c r="Y108" t="s">
-        <v>698</v>
-      </c>
-      <c r="Z108" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA108" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AB108" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="109" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC108" t="s">
+        <v>701</v>
+      </c>
+      <c r="AD108" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="109" spans="1:30">
       <c r="A109">
         <v>2538561</v>
       </c>
@@ -8497,37 +8509,37 @@
         <v>2023</v>
       </c>
       <c r="H109" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="I109" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="J109" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="K109" t="s">
-        <v>703</v>
-      </c>
-      <c r="W109" t="s">
-        <v>32</v>
-      </c>
-      <c r="X109" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="Y109" t="s">
-        <v>705</v>
+        <v>34</v>
       </c>
       <c r="Z109" t="s">
-        <v>35</v>
+        <v>706</v>
       </c>
       <c r="AA109" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AB109" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="110" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC109" t="s">
+        <v>708</v>
+      </c>
+      <c r="AD109" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="110" spans="1:30">
       <c r="A110">
         <v>2539461</v>
       </c>
@@ -8550,34 +8562,34 @@
         <v>2023</v>
       </c>
       <c r="H110" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="I110" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="J110" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="K110" t="s">
-        <v>710</v>
-      </c>
-      <c r="W110" t="s">
-        <v>32</v>
+        <v>712</v>
       </c>
       <c r="Y110" t="s">
-        <v>711</v>
-      </c>
-      <c r="Z110" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA110" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AB110" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="111" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC110" t="s">
+        <v>714</v>
+      </c>
+      <c r="AD110" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="111" spans="1:30">
       <c r="A111">
         <v>2540256</v>
       </c>
@@ -8600,34 +8612,34 @@
         <v>2023</v>
       </c>
       <c r="H111" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="I111" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="J111" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="K111" t="s">
-        <v>716</v>
-      </c>
-      <c r="W111" t="s">
-        <v>32</v>
+        <v>718</v>
       </c>
       <c r="Y111" t="s">
-        <v>717</v>
-      </c>
-      <c r="Z111" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA111" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AB111" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="112" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC111" t="s">
+        <v>720</v>
+      </c>
+      <c r="AD111" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="112" spans="1:30">
       <c r="A112">
         <v>2540818</v>
       </c>
@@ -8650,34 +8662,34 @@
         <v>2023</v>
       </c>
       <c r="H112" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="I112" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="J112" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="K112" t="s">
-        <v>722</v>
-      </c>
-      <c r="W112" t="s">
-        <v>32</v>
+        <v>724</v>
       </c>
       <c r="Y112" t="s">
-        <v>723</v>
-      </c>
-      <c r="Z112" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA112" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AB112" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="113" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC112" t="s">
+        <v>726</v>
+      </c>
+      <c r="AD112" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="113" spans="1:30">
       <c r="A113">
         <v>2541820</v>
       </c>
@@ -8700,34 +8712,34 @@
         <v>2023</v>
       </c>
       <c r="H113" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="I113" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="J113" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="K113" t="s">
-        <v>728</v>
-      </c>
-      <c r="W113" t="s">
-        <v>32</v>
+        <v>730</v>
       </c>
       <c r="Y113" t="s">
-        <v>729</v>
-      </c>
-      <c r="Z113" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA113" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AB113" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="114" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC113" t="s">
+        <v>732</v>
+      </c>
+      <c r="AD113" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="114" spans="1:30">
       <c r="A114">
         <v>2542472</v>
       </c>
@@ -8750,34 +8762,34 @@
         <v>2023</v>
       </c>
       <c r="H114" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="I114" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="J114" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="K114" t="s">
-        <v>734</v>
-      </c>
-      <c r="W114" t="s">
-        <v>32</v>
+        <v>736</v>
       </c>
       <c r="Y114" t="s">
-        <v>735</v>
-      </c>
-      <c r="Z114" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA114" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AB114" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="115" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC114" t="s">
+        <v>738</v>
+      </c>
+      <c r="AD114" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="115" spans="1:30">
       <c r="A115">
         <v>2543513</v>
       </c>
@@ -8800,34 +8812,34 @@
         <v>2023</v>
       </c>
       <c r="H115" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="I115" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="J115" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="K115" t="s">
-        <v>740</v>
-      </c>
-      <c r="W115" t="s">
-        <v>32</v>
+        <v>742</v>
       </c>
       <c r="Y115" t="s">
-        <v>741</v>
-      </c>
-      <c r="Z115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA115" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AB115" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="116" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC115" t="s">
+        <v>744</v>
+      </c>
+      <c r="AD115" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="116" spans="1:30">
       <c r="A116">
         <v>2544388</v>
       </c>
@@ -8850,34 +8862,34 @@
         <v>2023</v>
       </c>
       <c r="H116" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="I116" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="J116" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="K116" t="s">
-        <v>746</v>
-      </c>
-      <c r="W116" t="s">
-        <v>32</v>
+        <v>748</v>
       </c>
       <c r="Y116" t="s">
-        <v>747</v>
-      </c>
-      <c r="Z116" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA116" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AB116" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="117" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC116" t="s">
+        <v>750</v>
+      </c>
+      <c r="AD116" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="117" spans="1:30">
       <c r="A117">
         <v>2545135</v>
       </c>
@@ -8900,34 +8912,34 @@
         <v>2023</v>
       </c>
       <c r="H117" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="I117" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="J117" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="K117" t="s">
-        <v>752</v>
-      </c>
-      <c r="W117" t="s">
-        <v>32</v>
+        <v>754</v>
       </c>
       <c r="Y117" t="s">
-        <v>753</v>
-      </c>
-      <c r="Z117" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA117" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AB117" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="118" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC117" t="s">
+        <v>756</v>
+      </c>
+      <c r="AD117" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="118" spans="1:30">
       <c r="A118">
         <v>2545882</v>
       </c>
@@ -8950,34 +8962,34 @@
         <v>2023</v>
       </c>
       <c r="H118" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="I118" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="J118" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="K118" t="s">
-        <v>758</v>
-      </c>
-      <c r="W118" t="s">
-        <v>32</v>
+        <v>760</v>
       </c>
       <c r="Y118" t="s">
-        <v>759</v>
-      </c>
-      <c r="Z118" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA118" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AB118" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="119" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC118" t="s">
+        <v>762</v>
+      </c>
+      <c r="AD118" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="119" spans="1:30">
       <c r="A119">
         <v>2546748</v>
       </c>
@@ -9000,34 +9012,34 @@
         <v>2023</v>
       </c>
       <c r="H119" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="I119" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="J119" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="K119" t="s">
-        <v>764</v>
-      </c>
-      <c r="W119" t="s">
-        <v>32</v>
+        <v>766</v>
       </c>
       <c r="Y119" t="s">
-        <v>765</v>
-      </c>
-      <c r="Z119" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA119" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AB119" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="120" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC119" t="s">
+        <v>768</v>
+      </c>
+      <c r="AD119" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="120" spans="1:30">
       <c r="A120">
         <v>2547406</v>
       </c>
@@ -9050,34 +9062,34 @@
         <v>2023</v>
       </c>
       <c r="H120" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I120" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="J120" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="K120" t="s">
-        <v>770</v>
-      </c>
-      <c r="W120" t="s">
-        <v>32</v>
+        <v>772</v>
       </c>
       <c r="Y120" t="s">
-        <v>771</v>
-      </c>
-      <c r="Z120" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA120" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AB120" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="121" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC120" t="s">
+        <v>774</v>
+      </c>
+      <c r="AD120" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="121" spans="1:30">
       <c r="A121">
         <v>2547868</v>
       </c>
@@ -9100,34 +9112,34 @@
         <v>2023</v>
       </c>
       <c r="H121" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="I121" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="J121" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="K121" t="s">
-        <v>776</v>
-      </c>
-      <c r="W121" t="s">
-        <v>32</v>
+        <v>778</v>
       </c>
       <c r="Y121" t="s">
-        <v>777</v>
-      </c>
-      <c r="Z121" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA121" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AB121" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="122" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC121" t="s">
+        <v>780</v>
+      </c>
+      <c r="AD121" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="122" spans="1:30">
       <c r="A122">
         <v>2567815</v>
       </c>
@@ -9150,37 +9162,37 @@
         <v>2023</v>
       </c>
       <c r="H122" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="I122" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="J122" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="K122" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="N122" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="O122">
         <v>6</v>
       </c>
-      <c r="W122" t="s">
-        <v>32</v>
-      </c>
       <c r="Y122" t="s">
-        <v>783</v>
-      </c>
-      <c r="Z122" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA122" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="123" spans="1:28">
+        <v>785</v>
+      </c>
+      <c r="AB122" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC122" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="123" spans="1:30">
       <c r="A123">
         <v>2549642</v>
       </c>
@@ -9203,31 +9215,31 @@
         <v>2023</v>
       </c>
       <c r="H123" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="I123" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="K123" t="s">
-        <v>786</v>
-      </c>
-      <c r="W123" t="s">
-        <v>32</v>
+        <v>788</v>
       </c>
       <c r="Y123" t="s">
-        <v>787</v>
-      </c>
-      <c r="Z123" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA123" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AB123" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="124" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC123" t="s">
+        <v>790</v>
+      </c>
+      <c r="AD123" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="124" spans="1:30">
       <c r="A124">
         <v>2550342</v>
       </c>
@@ -9250,34 +9262,34 @@
         <v>2023</v>
       </c>
       <c r="H124" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="I124" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="J124" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="K124" t="s">
-        <v>791</v>
-      </c>
-      <c r="W124" t="s">
-        <v>32</v>
+        <v>793</v>
       </c>
       <c r="Y124" t="s">
-        <v>792</v>
-      </c>
-      <c r="Z124" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA124" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AB124" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="125" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC124" t="s">
+        <v>795</v>
+      </c>
+      <c r="AD124" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="125" spans="1:30">
       <c r="A125">
         <v>2551007</v>
       </c>
@@ -9300,34 +9312,34 @@
         <v>2023</v>
       </c>
       <c r="H125" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="I125" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="J125" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="K125" t="s">
-        <v>797</v>
-      </c>
-      <c r="W125" t="s">
-        <v>32</v>
+        <v>799</v>
       </c>
       <c r="Y125" t="s">
-        <v>798</v>
-      </c>
-      <c r="Z125" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA125" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AB125" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="126" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC125" t="s">
+        <v>801</v>
+      </c>
+      <c r="AD125" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="126" spans="1:30">
       <c r="A126">
         <v>2551793</v>
       </c>
@@ -9350,34 +9362,34 @@
         <v>2023</v>
       </c>
       <c r="H126" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="I126" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="J126" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="K126" t="s">
-        <v>803</v>
-      </c>
-      <c r="W126" t="s">
-        <v>32</v>
+        <v>805</v>
       </c>
       <c r="Y126" t="s">
-        <v>804</v>
-      </c>
-      <c r="Z126" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA126" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AB126" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="127" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC126" t="s">
+        <v>807</v>
+      </c>
+      <c r="AD126" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="127" spans="1:30">
       <c r="A127">
         <v>2552464</v>
       </c>
@@ -9400,34 +9412,34 @@
         <v>2023</v>
       </c>
       <c r="H127" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="I127" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="J127" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="K127" t="s">
-        <v>809</v>
-      </c>
-      <c r="W127" t="s">
-        <v>32</v>
+        <v>811</v>
       </c>
       <c r="Y127" t="s">
-        <v>810</v>
-      </c>
-      <c r="Z127" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA127" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AB127" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="128" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC127" t="s">
+        <v>813</v>
+      </c>
+      <c r="AD127" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="128" spans="1:30">
       <c r="A128">
         <v>2553351</v>
       </c>
@@ -9450,34 +9462,34 @@
         <v>2023</v>
       </c>
       <c r="H128" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="I128" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="J128" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="K128" t="s">
-        <v>815</v>
-      </c>
-      <c r="W128" t="s">
-        <v>32</v>
+        <v>817</v>
       </c>
       <c r="Y128" t="s">
-        <v>816</v>
-      </c>
-      <c r="Z128" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA128" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AB128" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="129" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC128" t="s">
+        <v>819</v>
+      </c>
+      <c r="AD128" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="129" spans="1:30">
       <c r="A129">
         <v>2554039</v>
       </c>
@@ -9500,34 +9512,34 @@
         <v>2023</v>
       </c>
       <c r="H129" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="I129" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="J129" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="K129" t="s">
-        <v>821</v>
-      </c>
-      <c r="W129" t="s">
-        <v>32</v>
+        <v>823</v>
       </c>
       <c r="Y129" t="s">
-        <v>822</v>
-      </c>
-      <c r="Z129" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA129" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AB129" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="130" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC129" t="s">
+        <v>825</v>
+      </c>
+      <c r="AD129" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="130" spans="1:30">
       <c r="A130">
         <v>2554483</v>
       </c>
@@ -9550,31 +9562,31 @@
         <v>2023</v>
       </c>
       <c r="H130" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="I130" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="J130" t="s">
-        <v>826</v>
-      </c>
-      <c r="W130" t="s">
-        <v>32</v>
+        <v>828</v>
       </c>
       <c r="Y130" t="s">
-        <v>827</v>
-      </c>
-      <c r="Z130" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA130" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AB130" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="131" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC130" t="s">
+        <v>830</v>
+      </c>
+      <c r="AD130" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="131" spans="1:30">
       <c r="A131">
         <v>2557350</v>
       </c>
@@ -9597,31 +9609,31 @@
         <v>2023</v>
       </c>
       <c r="H131" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="I131" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="J131" t="s">
-        <v>831</v>
-      </c>
-      <c r="W131" t="s">
-        <v>32</v>
+        <v>833</v>
       </c>
       <c r="Y131" t="s">
-        <v>832</v>
-      </c>
-      <c r="Z131" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA131" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="AB131" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="132" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC131" t="s">
+        <v>835</v>
+      </c>
+      <c r="AD131" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="132" spans="1:30">
       <c r="A132">
         <v>2567814</v>
       </c>
@@ -9644,40 +9656,40 @@
         <v>2023</v>
       </c>
       <c r="H132" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="I132" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="J132" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="K132" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="N132" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="O132">
         <v>5</v>
       </c>
-      <c r="W132" t="s">
-        <v>32</v>
-      </c>
       <c r="Y132" t="s">
-        <v>838</v>
-      </c>
-      <c r="Z132" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA132" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AB132" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="133" spans="1:28">
+        <v>37</v>
+      </c>
+      <c r="AC132" t="s">
+        <v>841</v>
+      </c>
+      <c r="AD132" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="133" spans="1:30">
       <c r="A133">
         <v>2567813</v>
       </c>
@@ -9700,37 +9712,37 @@
         <v>2023</v>
       </c>
       <c r="H133" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="I133" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="J133" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="K133" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="N133" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="O133">
         <v>5</v>
       </c>
-      <c r="W133" t="s">
-        <v>32</v>
-      </c>
       <c r="Y133" t="s">
-        <v>844</v>
-      </c>
-      <c r="Z133" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA133" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AB133" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="AC133" t="s">
+        <v>847</v>
+      </c>
+      <c r="AD133" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/raw/trektellen/Trektellen_headerdata_2422_2023.xlsx
+++ b/raw/trektellen/Trektellen_headerdata_2422_2023.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="849">
   <si>
     <t>id</t>
   </si>
@@ -2363,7 +2363,7 @@
     <t>2023-11-11 07:40:00</t>
   </si>
   <si>
-    <t>2023-11-11 19:14:00</t>
+    <t>2023-11-11 17:15:00</t>
   </si>
   <si>
     <t>Dominique Maire, Pascal Charrière 7h30/17h15,Raymond Bedouet 10h45/12h15, Andrée Tieffenbach 11h/15h40, Lutz Lucker et Sylvie Freymond 12h25/17h, Isabelle et Roger Cattin Gasser 13h/17h15</t>
@@ -2373,6 +2373,9 @@
   </si>
   <si>
     <t>2023-12-07 17:29:07.36437</t>
+  </si>
+  <si>
+    <t>2026-10-14 17:38:24.600072</t>
   </si>
   <si>
     <t>2023-11-12 07:19:00</t>
@@ -9189,7 +9192,10 @@
         <v>37</v>
       </c>
       <c r="AC122" t="s">
-        <v>785</v>
+        <v>786</v>
+      </c>
+      <c r="AD122" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="123" spans="1:30">
@@ -9215,25 +9221,25 @@
         <v>2023</v>
       </c>
       <c r="H123" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="I123" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="K123" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="Y123" t="s">
         <v>34</v>
       </c>
       <c r="AA123" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AB123" t="s">
         <v>37</v>
       </c>
       <c r="AC123" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AD123" t="s">
         <v>37</v>
@@ -9262,28 +9268,28 @@
         <v>2023</v>
       </c>
       <c r="H124" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="I124" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="J124" t="s">
         <v>651</v>
       </c>
       <c r="K124" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="Y124" t="s">
         <v>34</v>
       </c>
       <c r="AA124" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AB124" t="s">
         <v>37</v>
       </c>
       <c r="AC124" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AD124" t="s">
         <v>37</v>
@@ -9312,28 +9318,28 @@
         <v>2023</v>
       </c>
       <c r="H125" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="I125" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="J125" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="K125" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="Y125" t="s">
         <v>34</v>
       </c>
       <c r="AA125" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AB125" t="s">
         <v>37</v>
       </c>
       <c r="AC125" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AD125" t="s">
         <v>37</v>
@@ -9362,28 +9368,28 @@
         <v>2023</v>
       </c>
       <c r="H126" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="I126" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="J126" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="K126" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="Y126" t="s">
         <v>34</v>
       </c>
       <c r="AA126" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AB126" t="s">
         <v>37</v>
       </c>
       <c r="AC126" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AD126" t="s">
         <v>37</v>
@@ -9412,28 +9418,28 @@
         <v>2023</v>
       </c>
       <c r="H127" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="I127" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="J127" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="K127" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="Y127" t="s">
         <v>34</v>
       </c>
       <c r="AA127" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AB127" t="s">
         <v>37</v>
       </c>
       <c r="AC127" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AD127" t="s">
         <v>37</v>
@@ -9462,28 +9468,28 @@
         <v>2023</v>
       </c>
       <c r="H128" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="I128" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="J128" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="K128" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="Y128" t="s">
         <v>34</v>
       </c>
       <c r="AA128" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AB128" t="s">
         <v>37</v>
       </c>
       <c r="AC128" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AD128" t="s">
         <v>37</v>
@@ -9512,28 +9518,28 @@
         <v>2023</v>
       </c>
       <c r="H129" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I129" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="J129" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="K129" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="Y129" t="s">
         <v>34</v>
       </c>
       <c r="AA129" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AB129" t="s">
         <v>37</v>
       </c>
       <c r="AC129" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AD129" t="s">
         <v>37</v>
@@ -9562,25 +9568,25 @@
         <v>2023</v>
       </c>
       <c r="H130" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="I130" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="J130" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="Y130" t="s">
         <v>34</v>
       </c>
       <c r="AA130" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AB130" t="s">
         <v>37</v>
       </c>
       <c r="AC130" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AD130" t="s">
         <v>37</v>
@@ -9609,25 +9615,25 @@
         <v>2023</v>
       </c>
       <c r="H131" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="I131" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="J131" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="Y131" t="s">
         <v>34</v>
       </c>
       <c r="AA131" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AB131" t="s">
         <v>37</v>
       </c>
       <c r="AC131" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AD131" t="s">
         <v>37</v>
@@ -9656,16 +9662,16 @@
         <v>2023</v>
       </c>
       <c r="H132" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="I132" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="J132" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="K132" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="N132" t="s">
         <v>665</v>
@@ -9677,13 +9683,13 @@
         <v>34</v>
       </c>
       <c r="AA132" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AB132" t="s">
         <v>37</v>
       </c>
       <c r="AC132" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AD132" t="s">
         <v>37</v>
@@ -9712,16 +9718,16 @@
         <v>2023</v>
       </c>
       <c r="H133" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="I133" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="J133" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="K133" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="N133" t="s">
         <v>493</v>
@@ -9733,13 +9739,13 @@
         <v>34</v>
       </c>
       <c r="AA133" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AB133" t="s">
         <v>37</v>
       </c>
       <c r="AC133" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="AD133" t="s">
         <v>37</v>
